--- a/data/excel/real_road_construction_master.xlsx
+++ b/data/excel/real_road_construction_master.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="master" sheetId="1" r:id="R0a9f7fec2ead46f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="app_feature_map" sheetId="2" r:id="Ra247f059091741a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="3" r:id="R12762fe412094857"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="guide" sheetId="4" r:id="Rcc10a966c3f34dd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="master" sheetId="1" r:id="Rb40c306fbb5c43bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="app_feature_map" sheetId="2" r:id="Rdaa4604751a8496f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="3" r:id="Re9dbea97fe0845bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="guide" sheetId="4" r:id="Rf4986cf608ed4a89"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1247,7 +1247,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="S16" s="4" t="str">
-        <x:v>R-SHOIN-15; R-SHOIN-15; R-SHOIN-15; R-SHOIN-15; R-SHOIN-15; R-SHOIN-15; R-SHOIN-15</x:v>
+        <x:v>R-REAL-15; R-REAL-15; R-REAL-15; R-REAL-15; R-REAL-15; R-REAL-15; R-REAL-15</x:v>
       </x:c>
       <x:c r="T16" s="4" t="str">
         <x:v>188; 189; 190; 192; 193; 194; 195</x:v>
@@ -1324,7 +1324,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S17" s="4" t="str">
-        <x:v>R-SHOIN-16; R-SHOIN-16</x:v>
+        <x:v>R-REAL-16; R-REAL-16</x:v>
       </x:c>
       <x:c r="T17" s="4" t="str">
         <x:v>196; 197</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S18" s="4" t="str">
-        <x:v>R-SHOIN-17; R-SHOIN-17</x:v>
+        <x:v>R-REAL-17; R-REAL-17</x:v>
       </x:c>
       <x:c r="T18" s="4" t="str">
         <x:v>74; 75</x:v>
@@ -1478,7 +1478,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="S19" s="4" t="str">
-        <x:v>R-SHOIN-18; R-SHOIN-18; R-SHOIN-18; R-SHOIN-18; R-SHOIN-18</x:v>
+        <x:v>R-REAL-18; R-REAL-18; R-REAL-18; R-REAL-18; R-REAL-18</x:v>
       </x:c>
       <x:c r="T19" s="4" t="str">
         <x:v>76; 77; 78; 79; 80</x:v>
@@ -1555,7 +1555,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="S20" s="4" t="str">
-        <x:v>R-SHOIN-19; R-SHOIN-19; R-SHOIN-19; R-SHOIN-19; R-SHOIN-19; R-SHOIN-19; R-SHOIN-19; R-SHOIN-19; R-SHOIN-19; R-SHOIN-19; R-SHOIN-19; R-SHOIN-19; R-SHOIN-19; R-SHOIN-19; R-SHOIN-19; R-SHOIN-19; R-SHOIN-19; R-SHOIN-19</x:v>
+        <x:v>R-REAL-19; R-REAL-19; R-REAL-19; R-REAL-19; R-REAL-19; R-REAL-19; R-REAL-19; R-REAL-19; R-REAL-19; R-REAL-19; R-REAL-19; R-REAL-19; R-REAL-19; R-REAL-19; R-REAL-19; R-REAL-19; R-REAL-19; R-REAL-19</x:v>
       </x:c>
       <x:c r="T20" s="4" t="str">
         <x:v>81; 82; 83; 84; 85; 86; 87; 88; 89; 90; 91; 92; 93; 94; 95; 96; 97; 98</x:v>
@@ -1632,7 +1632,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="S21" s="4" t="str">
-        <x:v>R-SHOIN-20; R-SHOIN-20; R-SHOIN-20; R-SHOIN-20; R-SHOIN-20; R-SHOIN-20; R-SHOIN-20; R-SHOIN-20</x:v>
+        <x:v>R-REAL-20; R-REAL-20; R-REAL-20; R-REAL-20; R-REAL-20; R-REAL-20; R-REAL-20; R-REAL-20</x:v>
       </x:c>
       <x:c r="T21" s="4" t="str">
         <x:v>99; 100; 101; 102; 103; 104; 105; 106</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="S22" s="4" t="str">
-        <x:v>R-SHOIN-21; R-SHOIN-21; R-SHOIN-21; R-SHOIN-21; R-SHOIN-21; R-SHOIN-21</x:v>
+        <x:v>R-REAL-21; R-REAL-21; R-REAL-21; R-REAL-21; R-REAL-21; R-REAL-21</x:v>
       </x:c>
       <x:c r="T22" s="4" t="str">
         <x:v>107; 109; 110; 111; 112; 113</x:v>
@@ -1849,7 +1849,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S24" s="4" t="str">
-        <x:v>R-SHOIN-23</x:v>
+        <x:v>R-REAL-23</x:v>
       </x:c>
       <x:c r="T24" s="4" t="str">
         <x:v>114</x:v>
@@ -1926,7 +1926,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S25" s="4" t="str">
-        <x:v>R-SHOIN-24</x:v>
+        <x:v>R-REAL-24</x:v>
       </x:c>
       <x:c r="T25" s="4" t="str">
         <x:v>127</x:v>
@@ -2003,7 +2003,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S26" s="4" t="str">
-        <x:v>R-SHOIN-25; R-SHOIN-25</x:v>
+        <x:v>R-REAL-25; R-REAL-25</x:v>
       </x:c>
       <x:c r="T26" s="4" t="str">
         <x:v>130; 131</x:v>
@@ -2080,7 +2080,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S27" s="4" t="str">
-        <x:v>R-SHOIN-26</x:v>
+        <x:v>R-REAL-26</x:v>
       </x:c>
       <x:c r="T27" s="4" t="str">
         <x:v>123</x:v>
@@ -2157,7 +2157,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S28" s="4" t="str">
-        <x:v>R-SHOIN-27</x:v>
+        <x:v>R-REAL-27</x:v>
       </x:c>
       <x:c r="T28" s="4" t="str">
         <x:v>159</x:v>
@@ -2234,7 +2234,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S29" s="4" t="str">
-        <x:v>R-SHOIN-28</x:v>
+        <x:v>R-REAL-28</x:v>
       </x:c>
       <x:c r="T29" s="4" t="str">
         <x:v>139</x:v>
@@ -2374,7 +2374,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S31" s="4" t="str">
-        <x:v>R-SHOIN-30</x:v>
+        <x:v>R-REAL-30</x:v>
       </x:c>
       <x:c r="T31" s="4" t="str">
         <x:v>118</x:v>
@@ -2451,7 +2451,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S32" s="4" t="str">
-        <x:v>R-SHOIN-31</x:v>
+        <x:v>R-REAL-31</x:v>
       </x:c>
       <x:c r="T32" s="4" t="str">
         <x:v>122</x:v>
@@ -2528,7 +2528,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S33" s="4" t="str">
-        <x:v>R-SHOIN-32</x:v>
+        <x:v>R-REAL-32</x:v>
       </x:c>
       <x:c r="T33" s="4" t="str">
         <x:v>120</x:v>
@@ -2605,7 +2605,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S34" s="4" t="str">
-        <x:v>R-SHOIN-33</x:v>
+        <x:v>R-REAL-33</x:v>
       </x:c>
       <x:c r="T34" s="4" t="str">
         <x:v>128</x:v>
@@ -2682,7 +2682,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S35" s="4" t="str">
-        <x:v>R-SHOIN-34</x:v>
+        <x:v>R-REAL-34</x:v>
       </x:c>
       <x:c r="T35" s="4" t="str">
         <x:v>129</x:v>
@@ -2822,7 +2822,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S37" s="4" t="str">
-        <x:v>R-SHOIN-36</x:v>
+        <x:v>R-REAL-36</x:v>
       </x:c>
       <x:c r="T37" s="4" t="str">
         <x:v>142</x:v>
@@ -2899,7 +2899,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S38" s="4" t="str">
-        <x:v>R-SHOIN-37</x:v>
+        <x:v>R-REAL-37</x:v>
       </x:c>
       <x:c r="T38" s="4" t="str">
         <x:v>124</x:v>
@@ -2976,7 +2976,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S39" s="4" t="str">
-        <x:v>R-SHOIN-38</x:v>
+        <x:v>R-REAL-38</x:v>
       </x:c>
       <x:c r="T39" s="4" t="str">
         <x:v>145</x:v>
@@ -3053,7 +3053,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S40" s="4" t="str">
-        <x:v>R-SHOIN-39</x:v>
+        <x:v>R-REAL-39</x:v>
       </x:c>
       <x:c r="T40" s="4" t="str">
         <x:v>135</x:v>
@@ -3130,7 +3130,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S41" s="4" t="str">
-        <x:v>R-SHOIN-40</x:v>
+        <x:v>R-REAL-40</x:v>
       </x:c>
       <x:c r="T41" s="4" t="str">
         <x:v>155</x:v>
@@ -3207,7 +3207,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S42" s="4" t="str">
-        <x:v>R-SHOIN-41</x:v>
+        <x:v>R-REAL-41</x:v>
       </x:c>
       <x:c r="T42" s="4" t="str">
         <x:v>137</x:v>
@@ -3284,7 +3284,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S43" s="4" t="str">
-        <x:v>R-SHOIN-42</x:v>
+        <x:v>R-REAL-42</x:v>
       </x:c>
       <x:c r="T43" s="4" t="str">
         <x:v>136</x:v>
@@ -3361,7 +3361,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S44" s="4" t="str">
-        <x:v>R-SHOIN-43</x:v>
+        <x:v>R-REAL-43</x:v>
       </x:c>
       <x:c r="T44" s="4" t="str">
         <x:v>143</x:v>
@@ -3438,7 +3438,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S45" s="4" t="str">
-        <x:v>R-SHOIN-44</x:v>
+        <x:v>R-REAL-44</x:v>
       </x:c>
       <x:c r="T45" s="4" t="str">
         <x:v>141</x:v>
@@ -3515,7 +3515,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S46" s="4" t="str">
-        <x:v>R-SHOIN-45</x:v>
+        <x:v>R-REAL-45</x:v>
       </x:c>
       <x:c r="T46" s="4" t="str">
         <x:v>126</x:v>
@@ -3592,7 +3592,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S47" s="4" t="str">
-        <x:v>R-SHOIN-46</x:v>
+        <x:v>R-REAL-46</x:v>
       </x:c>
       <x:c r="T47" s="4" t="str">
         <x:v>146</x:v>
@@ -3669,7 +3669,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S48" s="4" t="str">
-        <x:v>R-SHOIN-47</x:v>
+        <x:v>R-REAL-47</x:v>
       </x:c>
       <x:c r="T48" s="4" t="str">
         <x:v>147</x:v>
@@ -3746,7 +3746,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S49" s="4" t="str">
-        <x:v>R-SHOIN-48</x:v>
+        <x:v>R-REAL-48</x:v>
       </x:c>
       <x:c r="T49" s="4" t="str">
         <x:v>148</x:v>
@@ -3815,7 +3815,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S50" s="4" t="str">
-        <x:v>R-SHOIN-309</x:v>
+        <x:v>R-REAL-309</x:v>
       </x:c>
       <x:c r="T50" s="4" t="str">
         <x:v>149</x:v>
@@ -3892,7 +3892,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S51" s="4" t="str">
-        <x:v>R-SHOIN-49</x:v>
+        <x:v>R-REAL-49</x:v>
       </x:c>
       <x:c r="T51" s="4" t="str">
         <x:v>138</x:v>
@@ -3969,7 +3969,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S52" s="4" t="str">
-        <x:v>R-SHOIN-50</x:v>
+        <x:v>R-REAL-50</x:v>
       </x:c>
       <x:c r="T52" s="4" t="str">
         <x:v>152</x:v>
@@ -4046,7 +4046,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S53" s="4" t="str">
-        <x:v>R-SHOIN-51</x:v>
+        <x:v>R-REAL-51</x:v>
       </x:c>
       <x:c r="T53" s="4" t="str">
         <x:v>151</x:v>
@@ -4123,7 +4123,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S54" s="4" t="str">
-        <x:v>R-SHOIN-52</x:v>
+        <x:v>R-REAL-52</x:v>
       </x:c>
       <x:c r="T54" s="4" t="str">
         <x:v>116</x:v>
@@ -4200,7 +4200,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S55" s="4" t="str">
-        <x:v>R-SHOIN-53</x:v>
+        <x:v>R-REAL-53</x:v>
       </x:c>
       <x:c r="T55" s="4" t="str">
         <x:v>156</x:v>
@@ -4277,7 +4277,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S56" s="4" t="str">
-        <x:v>R-SHOIN-54</x:v>
+        <x:v>R-REAL-54</x:v>
       </x:c>
       <x:c r="T56" s="4" t="str">
         <x:v>132</x:v>
@@ -4354,7 +4354,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S57" s="4" t="str">
-        <x:v>R-SHOIN-55</x:v>
+        <x:v>R-REAL-55</x:v>
       </x:c>
       <x:c r="T57" s="4" t="str">
         <x:v>153</x:v>
@@ -4431,7 +4431,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S58" s="4" t="str">
-        <x:v>R-SHOIN-56</x:v>
+        <x:v>R-REAL-56</x:v>
       </x:c>
       <x:c r="T58" s="4" t="str">
         <x:v>157</x:v>
@@ -4508,7 +4508,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S59" s="4" t="str">
-        <x:v>R-SHOIN-57</x:v>
+        <x:v>R-REAL-57</x:v>
       </x:c>
       <x:c r="T59" s="4" t="str">
         <x:v>125</x:v>
@@ -4585,7 +4585,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S60" s="4" t="str">
-        <x:v>R-SHOIN-58</x:v>
+        <x:v>R-REAL-58</x:v>
       </x:c>
       <x:c r="T60" s="4" t="str">
         <x:v>117</x:v>
@@ -4662,7 +4662,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S61" s="4" t="str">
-        <x:v>R-SHOIN-59</x:v>
+        <x:v>R-REAL-59</x:v>
       </x:c>
       <x:c r="T61" s="4" t="str">
         <x:v>154</x:v>
@@ -4739,7 +4739,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S62" s="4" t="str">
-        <x:v>R-SHOIN-60</x:v>
+        <x:v>R-REAL-60</x:v>
       </x:c>
       <x:c r="T62" s="4" t="str">
         <x:v>150</x:v>
@@ -4816,7 +4816,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S63" s="4" t="str">
-        <x:v>R-SHOIN-61</x:v>
+        <x:v>R-REAL-61</x:v>
       </x:c>
       <x:c r="T63" s="4" t="str">
         <x:v>115</x:v>
@@ -4893,7 +4893,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S64" s="4" t="str">
-        <x:v>R-SHOIN-62</x:v>
+        <x:v>R-REAL-62</x:v>
       </x:c>
       <x:c r="T64" s="4" t="str">
         <x:v>158</x:v>
@@ -4970,7 +4970,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S65" s="4" t="str">
-        <x:v>R-SHOIN-63</x:v>
+        <x:v>R-REAL-63</x:v>
       </x:c>
       <x:c r="T65" s="4" t="str">
         <x:v>121</x:v>
@@ -5047,7 +5047,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S66" s="4" t="str">
-        <x:v>R-SHOIN-64</x:v>
+        <x:v>R-REAL-64</x:v>
       </x:c>
       <x:c r="T66" s="4" t="str">
         <x:v>119</x:v>
@@ -5124,7 +5124,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S67" s="4" t="str">
-        <x:v>R-SHOIN-65; R-SHOIN-65</x:v>
+        <x:v>R-REAL-65; R-REAL-65</x:v>
       </x:c>
       <x:c r="T67" s="4" t="str">
         <x:v>133; 134</x:v>
@@ -5201,7 +5201,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S68" s="4" t="str">
-        <x:v>R-SHOIN-66</x:v>
+        <x:v>R-REAL-66</x:v>
       </x:c>
       <x:c r="T68" s="4" t="str">
         <x:v>140</x:v>
@@ -5278,7 +5278,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S69" s="4" t="str">
-        <x:v>R-SHOIN-67</x:v>
+        <x:v>R-REAL-67</x:v>
       </x:c>
       <x:c r="T69" s="4" t="str">
         <x:v>144</x:v>
@@ -5355,7 +5355,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S70" s="4" t="str">
-        <x:v>R-SHOIN-68</x:v>
+        <x:v>R-REAL-68</x:v>
       </x:c>
       <x:c r="T70" s="4" t="str">
         <x:v>171</x:v>
@@ -5432,7 +5432,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S71" s="4" t="str">
-        <x:v>R-SHOIN-69</x:v>
+        <x:v>R-REAL-69</x:v>
       </x:c>
       <x:c r="T71" s="4" t="str">
         <x:v>180</x:v>
@@ -5509,7 +5509,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="S72" s="4" t="str">
-        <x:v>R-SHOIN-70; R-SHOIN-70; R-SHOIN-70</x:v>
+        <x:v>R-REAL-70; R-REAL-70; R-REAL-70</x:v>
       </x:c>
       <x:c r="T72" s="4" t="str">
         <x:v>177; 178; 179</x:v>
@@ -5586,7 +5586,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S73" s="4" t="str">
-        <x:v>R-SHOIN-71</x:v>
+        <x:v>R-REAL-71</x:v>
       </x:c>
       <x:c r="T73" s="4" t="str">
         <x:v>187</x:v>
@@ -5663,7 +5663,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S74" s="4" t="str">
-        <x:v>R-SHOIN-72</x:v>
+        <x:v>R-REAL-72</x:v>
       </x:c>
       <x:c r="T74" s="4" t="str">
         <x:v>176</x:v>
@@ -5740,7 +5740,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S75" s="4" t="str">
-        <x:v>R-SHOIN-73</x:v>
+        <x:v>R-REAL-73</x:v>
       </x:c>
       <x:c r="T75" s="4" t="str">
         <x:v>174</x:v>
@@ -5817,7 +5817,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S76" s="4" t="str">
-        <x:v>R-SHOIN-74</x:v>
+        <x:v>R-REAL-74</x:v>
       </x:c>
       <x:c r="T76" s="4" t="str">
         <x:v>175</x:v>
@@ -5957,7 +5957,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S78" s="4" t="str">
-        <x:v>R-SHOIN-76</x:v>
+        <x:v>R-REAL-76</x:v>
       </x:c>
       <x:c r="T78" s="4" t="str">
         <x:v>173</x:v>
@@ -6034,7 +6034,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S79" s="4" t="str">
-        <x:v>R-SHOIN-77</x:v>
+        <x:v>R-REAL-77</x:v>
       </x:c>
       <x:c r="T79" s="4" t="str">
         <x:v>172</x:v>
@@ -6111,7 +6111,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S80" s="4" t="str">
-        <x:v>R-SHOIN-78</x:v>
+        <x:v>R-REAL-78</x:v>
       </x:c>
       <x:c r="T80" s="4" t="str">
         <x:v>186</x:v>
@@ -6178,7 +6178,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S81" s="4" t="str">
-        <x:v>R-SHOIN-310; R-SHOIN-310</x:v>
+        <x:v>R-REAL-310; R-REAL-310</x:v>
       </x:c>
       <x:c r="T81" s="4" t="str">
         <x:v>166; 167</x:v>
@@ -6255,7 +6255,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S82" s="4" t="str">
-        <x:v>R-SHOIN-79</x:v>
+        <x:v>R-REAL-79</x:v>
       </x:c>
       <x:c r="T82" s="4" t="str">
         <x:v>184</x:v>
@@ -6458,7 +6458,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="S85" s="4" t="str">
-        <x:v>R-SHOIN-82; R-SHOIN-82; R-SHOIN-82</x:v>
+        <x:v>R-REAL-82; R-REAL-82; R-REAL-82</x:v>
       </x:c>
       <x:c r="T85" s="4" t="str">
         <x:v>168; 169; 170</x:v>
@@ -6535,7 +6535,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S86" s="4" t="str">
-        <x:v>R-SHOIN-83</x:v>
+        <x:v>R-REAL-83</x:v>
       </x:c>
       <x:c r="T86" s="4" t="str">
         <x:v>165</x:v>
@@ -6612,7 +6612,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S87" s="4" t="str">
-        <x:v>R-SHOIN-84</x:v>
+        <x:v>R-REAL-84</x:v>
       </x:c>
       <x:c r="T87" s="4" t="str">
         <x:v>164</x:v>
@@ -6689,7 +6689,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S88" s="4" t="str">
-        <x:v>R-SHOIN-85</x:v>
+        <x:v>R-REAL-85</x:v>
       </x:c>
       <x:c r="T88" s="4" t="str">
         <x:v>163</x:v>
@@ -6766,7 +6766,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S89" s="4" t="str">
-        <x:v>R-SHOIN-86</x:v>
+        <x:v>R-REAL-86</x:v>
       </x:c>
       <x:c r="T89" s="4" t="str">
         <x:v>161</x:v>
@@ -6843,7 +6843,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S90" s="4" t="str">
-        <x:v>R-SHOIN-87</x:v>
+        <x:v>R-REAL-87</x:v>
       </x:c>
       <x:c r="T90" s="4" t="str">
         <x:v>162</x:v>
@@ -6920,7 +6920,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S91" s="4" t="str">
-        <x:v>R-SHOIN-88; R-SHOIN-88</x:v>
+        <x:v>R-REAL-88; R-REAL-88</x:v>
       </x:c>
       <x:c r="T91" s="4" t="str">
         <x:v>182; 183</x:v>
@@ -7251,7 +7251,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S96" s="4" t="str">
-        <x:v>R-SHOIN-93</x:v>
+        <x:v>R-REAL-93</x:v>
       </x:c>
       <x:c r="T96" s="4" t="str">
         <x:v>185</x:v>
@@ -15170,7 +15170,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="S223" s="4" t="str">
-        <x:v>R-SHOIN-220; R-SHOIN-220; R-SHOIN-220</x:v>
+        <x:v>R-REAL-220; R-REAL-220; R-REAL-220</x:v>
       </x:c>
       <x:c r="T223" s="4" t="str">
         <x:v>2; 3; 4</x:v>
@@ -15310,7 +15310,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S225" s="4" t="str">
-        <x:v>R-SHOIN-222</x:v>
+        <x:v>R-REAL-222</x:v>
       </x:c>
       <x:c r="T225" s="4" t="str">
         <x:v>5</x:v>
@@ -15387,7 +15387,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="S226" s="4" t="str">
-        <x:v>R-SHOIN-223; R-SHOIN-223; R-SHOIN-223</x:v>
+        <x:v>R-REAL-223; R-REAL-223; R-REAL-223</x:v>
       </x:c>
       <x:c r="T226" s="4" t="str">
         <x:v>6; 7; 8</x:v>
@@ -15464,7 +15464,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="S227" s="4" t="str">
-        <x:v>R-SHOIN-224; R-SHOIN-224; R-SHOIN-224; R-SHOIN-224; R-SHOIN-224; R-SHOIN-224; R-SHOIN-224; R-SHOIN-224; R-SHOIN-224</x:v>
+        <x:v>R-REAL-224; R-REAL-224; R-REAL-224; R-REAL-224; R-REAL-224; R-REAL-224; R-REAL-224; R-REAL-224; R-REAL-224</x:v>
       </x:c>
       <x:c r="T227" s="4" t="str">
         <x:v>9; 10; 11; 12; 13; 14; 15; 16; 17</x:v>
@@ -15541,7 +15541,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="S228" s="4" t="str">
-        <x:v>R-SHOIN-225; R-SHOIN-225; R-SHOIN-225; R-SHOIN-225; R-SHOIN-225; R-SHOIN-225; R-SHOIN-225; R-SHOIN-225; R-SHOIN-225; R-SHOIN-225</x:v>
+        <x:v>R-REAL-225; R-REAL-225; R-REAL-225; R-REAL-225; R-REAL-225; R-REAL-225; R-REAL-225; R-REAL-225; R-REAL-225; R-REAL-225</x:v>
       </x:c>
       <x:c r="T228" s="4" t="str">
         <x:v>18; 19; 20; 21; 22; 23; 24; 25; 26; 27</x:v>
@@ -15618,7 +15618,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="S229" s="4" t="str">
-        <x:v>R-SHOIN-226; R-SHOIN-226; R-SHOIN-226; R-SHOIN-226; R-SHOIN-226</x:v>
+        <x:v>R-REAL-226; R-REAL-226; R-REAL-226; R-REAL-226; R-REAL-226</x:v>
       </x:c>
       <x:c r="T229" s="4" t="str">
         <x:v>28; 29; 30; 31; 32</x:v>
@@ -15695,7 +15695,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S230" s="4" t="str">
-        <x:v>R-SHOIN-227</x:v>
+        <x:v>R-REAL-227</x:v>
       </x:c>
       <x:c r="T230" s="4" t="str">
         <x:v>33</x:v>
@@ -15772,7 +15772,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S231" s="4" t="str">
-        <x:v>R-SHOIN-228</x:v>
+        <x:v>R-REAL-228</x:v>
       </x:c>
       <x:c r="T231" s="4" t="str">
         <x:v>34</x:v>
@@ -15849,7 +15849,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S232" s="4" t="str">
-        <x:v>R-SHOIN-229</x:v>
+        <x:v>R-REAL-229</x:v>
       </x:c>
       <x:c r="T232" s="4" t="str">
         <x:v>35</x:v>
@@ -15926,7 +15926,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S233" s="4" t="str">
-        <x:v>R-SHOIN-230; R-SHOIN-230</x:v>
+        <x:v>R-REAL-230; R-REAL-230</x:v>
       </x:c>
       <x:c r="T233" s="4" t="str">
         <x:v>36; 37</x:v>
@@ -16003,7 +16003,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S234" s="4" t="str">
-        <x:v>R-SHOIN-231</x:v>
+        <x:v>R-REAL-231</x:v>
       </x:c>
       <x:c r="T234" s="4" t="str">
         <x:v>38</x:v>
@@ -16080,7 +16080,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S235" s="4" t="str">
-        <x:v>R-SHOIN-232; R-SHOIN-232</x:v>
+        <x:v>R-REAL-232; R-REAL-232</x:v>
       </x:c>
       <x:c r="T235" s="4" t="str">
         <x:v>42; 45</x:v>
@@ -16157,7 +16157,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S236" s="4" t="str">
-        <x:v>R-SHOIN-233</x:v>
+        <x:v>R-REAL-233</x:v>
       </x:c>
       <x:c r="T236" s="4" t="str">
         <x:v>48</x:v>
@@ -16234,7 +16234,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S237" s="4" t="str">
-        <x:v>R-SHOIN-234</x:v>
+        <x:v>R-REAL-234</x:v>
       </x:c>
       <x:c r="T237" s="4" t="str">
         <x:v>46</x:v>
@@ -16311,7 +16311,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S238" s="4" t="str">
-        <x:v>R-SHOIN-235</x:v>
+        <x:v>R-REAL-235</x:v>
       </x:c>
       <x:c r="T238" s="4" t="str">
         <x:v>47</x:v>
@@ -16388,7 +16388,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S239" s="4" t="str">
-        <x:v>R-SHOIN-236</x:v>
+        <x:v>R-REAL-236</x:v>
       </x:c>
       <x:c r="T239" s="4" t="str">
         <x:v>40</x:v>
@@ -16465,7 +16465,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S240" s="4" t="str">
-        <x:v>R-SHOIN-237; R-SHOIN-237</x:v>
+        <x:v>R-REAL-237; R-REAL-237</x:v>
       </x:c>
       <x:c r="T240" s="4" t="str">
         <x:v>43; 44</x:v>
@@ -16542,7 +16542,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S241" s="4" t="str">
-        <x:v>R-SHOIN-238</x:v>
+        <x:v>R-REAL-238</x:v>
       </x:c>
       <x:c r="T241" s="4" t="str">
         <x:v>41</x:v>
@@ -16619,7 +16619,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S242" s="4" t="str">
-        <x:v>R-SHOIN-239</x:v>
+        <x:v>R-REAL-239</x:v>
       </x:c>
       <x:c r="T242" s="4" t="str">
         <x:v>39</x:v>
@@ -16696,7 +16696,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S243" s="4" t="str">
-        <x:v>R-SHOIN-240</x:v>
+        <x:v>R-REAL-240</x:v>
       </x:c>
       <x:c r="T243" s="4" t="str">
         <x:v>50</x:v>
@@ -16773,7 +16773,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S244" s="4" t="str">
-        <x:v>R-SHOIN-241</x:v>
+        <x:v>R-REAL-241</x:v>
       </x:c>
       <x:c r="T244" s="4" t="str">
         <x:v>49</x:v>
@@ -16850,7 +16850,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S245" s="4" t="str">
-        <x:v>R-SHOIN-242</x:v>
+        <x:v>R-REAL-242</x:v>
       </x:c>
       <x:c r="T245" s="4" t="str">
         <x:v>52</x:v>
@@ -16927,7 +16927,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S246" s="4" t="str">
-        <x:v>R-SHOIN-243</x:v>
+        <x:v>R-REAL-243</x:v>
       </x:c>
       <x:c r="T246" s="4" t="str">
         <x:v>53</x:v>
@@ -17004,7 +17004,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S247" s="4" t="str">
-        <x:v>R-SHOIN-244</x:v>
+        <x:v>R-REAL-244</x:v>
       </x:c>
       <x:c r="T247" s="4" t="str">
         <x:v>54</x:v>
@@ -17081,7 +17081,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S248" s="4" t="str">
-        <x:v>R-SHOIN-245</x:v>
+        <x:v>R-REAL-245</x:v>
       </x:c>
       <x:c r="T248" s="4" t="str">
         <x:v>55</x:v>
@@ -17158,7 +17158,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S249" s="4" t="str">
-        <x:v>R-SHOIN-246</x:v>
+        <x:v>R-REAL-246</x:v>
       </x:c>
       <x:c r="T249" s="4" t="str">
         <x:v>51</x:v>
@@ -17235,7 +17235,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S250" s="4" t="str">
-        <x:v>R-SHOIN-247</x:v>
+        <x:v>R-REAL-247</x:v>
       </x:c>
       <x:c r="T250" s="4" t="str">
         <x:v>56</x:v>
@@ -17312,7 +17312,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S251" s="4" t="str">
-        <x:v>R-SHOIN-248</x:v>
+        <x:v>R-REAL-248</x:v>
       </x:c>
       <x:c r="T251" s="4" t="str">
         <x:v>57</x:v>
@@ -17389,7 +17389,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S252" s="4" t="str">
-        <x:v>R-SHOIN-249</x:v>
+        <x:v>R-REAL-249</x:v>
       </x:c>
       <x:c r="T252" s="4" t="str">
         <x:v>58</x:v>
@@ -17466,7 +17466,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S253" s="4" t="str">
-        <x:v>R-SHOIN-250</x:v>
+        <x:v>R-REAL-250</x:v>
       </x:c>
       <x:c r="T253" s="4" t="str">
         <x:v>73</x:v>
@@ -17669,7 +17669,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S256" s="4" t="str">
-        <x:v>R-SHOIN-253</x:v>
+        <x:v>R-REAL-253</x:v>
       </x:c>
       <x:c r="T256" s="4" t="str">
         <x:v>64</x:v>
@@ -17746,7 +17746,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="S257" s="4" t="str">
-        <x:v>R-SHOIN-254; R-SHOIN-254; R-SHOIN-254</x:v>
+        <x:v>R-REAL-254; R-REAL-254; R-REAL-254</x:v>
       </x:c>
       <x:c r="T257" s="4" t="str">
         <x:v>60; 61; 62</x:v>
@@ -17823,7 +17823,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S258" s="4" t="str">
-        <x:v>R-SHOIN-255</x:v>
+        <x:v>R-REAL-255</x:v>
       </x:c>
       <x:c r="T258" s="4" t="str">
         <x:v>63</x:v>
@@ -17900,7 +17900,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S259" s="4" t="str">
-        <x:v>R-SHOIN-256; R-SHOIN-256</x:v>
+        <x:v>R-REAL-256; R-REAL-256</x:v>
       </x:c>
       <x:c r="T259" s="4" t="str">
         <x:v>66; 67</x:v>
@@ -17977,7 +17977,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S260" s="4" t="str">
-        <x:v>R-SHOIN-257</x:v>
+        <x:v>R-REAL-257</x:v>
       </x:c>
       <x:c r="T260" s="4" t="str">
         <x:v>69</x:v>
@@ -18054,7 +18054,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S261" s="4" t="str">
-        <x:v>R-SHOIN-258</x:v>
+        <x:v>R-REAL-258</x:v>
       </x:c>
       <x:c r="T261" s="4" t="str">
         <x:v>72</x:v>
@@ -18131,7 +18131,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S262" s="4" t="str">
-        <x:v>R-SHOIN-259</x:v>
+        <x:v>R-REAL-259</x:v>
       </x:c>
       <x:c r="T262" s="4" t="str">
         <x:v>68</x:v>
@@ -18208,7 +18208,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S263" s="4" t="str">
-        <x:v>R-SHOIN-260</x:v>
+        <x:v>R-REAL-260</x:v>
       </x:c>
       <x:c r="T263" s="4" t="str">
         <x:v>59</x:v>
@@ -18285,7 +18285,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S264" s="4" t="str">
-        <x:v>R-SHOIN-261</x:v>
+        <x:v>R-REAL-261</x:v>
       </x:c>
       <x:c r="T264" s="4" t="str">
         <x:v>70</x:v>
@@ -18362,7 +18362,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S265" s="4" t="str">
-        <x:v>R-SHOIN-262</x:v>
+        <x:v>R-REAL-262</x:v>
       </x:c>
       <x:c r="T265" s="4" t="str">
         <x:v>65</x:v>
@@ -18439,7 +18439,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S266" s="4" t="str">
-        <x:v>R-SHOIN-263</x:v>
+        <x:v>R-REAL-263</x:v>
       </x:c>
       <x:c r="T266" s="4" t="str">
         <x:v>71</x:v>
@@ -21324,7 +21324,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="4" t="str">
-        <x:v>R-SHOIN-220</x:v>
+        <x:v>R-REAL-220</x:v>
       </x:c>
       <x:c r="B2" s="4" t="str">
         <x:v>220</x:v>
@@ -21365,7 +21365,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="4" t="str">
-        <x:v>R-SHOIN-220</x:v>
+        <x:v>R-REAL-220</x:v>
       </x:c>
       <x:c r="B3" s="4" t="str">
         <x:v>220</x:v>
@@ -21406,7 +21406,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="4" t="str">
-        <x:v>R-SHOIN-220</x:v>
+        <x:v>R-REAL-220</x:v>
       </x:c>
       <x:c r="B4" s="4" t="str">
         <x:v>220</x:v>
@@ -21447,7 +21447,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="4" t="str">
-        <x:v>R-SHOIN-222</x:v>
+        <x:v>R-REAL-222</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
         <x:v>222</x:v>
@@ -21488,7 +21488,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="4" t="str">
-        <x:v>R-SHOIN-223</x:v>
+        <x:v>R-REAL-223</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
         <x:v>223</x:v>
@@ -21529,7 +21529,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="4" t="str">
-        <x:v>R-SHOIN-223</x:v>
+        <x:v>R-REAL-223</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
         <x:v>223</x:v>
@@ -21570,7 +21570,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="4" t="str">
-        <x:v>R-SHOIN-223</x:v>
+        <x:v>R-REAL-223</x:v>
       </x:c>
       <x:c r="B8" s="4" t="str">
         <x:v>223</x:v>
@@ -21611,7 +21611,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="4" t="str">
-        <x:v>R-SHOIN-224</x:v>
+        <x:v>R-REAL-224</x:v>
       </x:c>
       <x:c r="B9" s="4" t="str">
         <x:v>224</x:v>
@@ -21652,7 +21652,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="4" t="str">
-        <x:v>R-SHOIN-224</x:v>
+        <x:v>R-REAL-224</x:v>
       </x:c>
       <x:c r="B10" s="4" t="str">
         <x:v>224</x:v>
@@ -21693,7 +21693,7 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="4" t="str">
-        <x:v>R-SHOIN-224</x:v>
+        <x:v>R-REAL-224</x:v>
       </x:c>
       <x:c r="B11" s="4" t="str">
         <x:v>224</x:v>
@@ -21734,7 +21734,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="4" t="str">
-        <x:v>R-SHOIN-224</x:v>
+        <x:v>R-REAL-224</x:v>
       </x:c>
       <x:c r="B12" s="4" t="str">
         <x:v>224</x:v>
@@ -21775,7 +21775,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="4" t="str">
-        <x:v>R-SHOIN-224</x:v>
+        <x:v>R-REAL-224</x:v>
       </x:c>
       <x:c r="B13" s="4" t="str">
         <x:v>224</x:v>
@@ -21816,7 +21816,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="4" t="str">
-        <x:v>R-SHOIN-224</x:v>
+        <x:v>R-REAL-224</x:v>
       </x:c>
       <x:c r="B14" s="4" t="str">
         <x:v>224</x:v>
@@ -21857,7 +21857,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="4" t="str">
-        <x:v>R-SHOIN-224</x:v>
+        <x:v>R-REAL-224</x:v>
       </x:c>
       <x:c r="B15" s="4" t="str">
         <x:v>224</x:v>
@@ -21898,7 +21898,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="4" t="str">
-        <x:v>R-SHOIN-224</x:v>
+        <x:v>R-REAL-224</x:v>
       </x:c>
       <x:c r="B16" s="4" t="str">
         <x:v>224</x:v>
@@ -21939,7 +21939,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="4" t="str">
-        <x:v>R-SHOIN-224</x:v>
+        <x:v>R-REAL-224</x:v>
       </x:c>
       <x:c r="B17" s="4" t="str">
         <x:v>224</x:v>
@@ -21980,7 +21980,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="4" t="str">
-        <x:v>R-SHOIN-225</x:v>
+        <x:v>R-REAL-225</x:v>
       </x:c>
       <x:c r="B18" s="4" t="str">
         <x:v>225</x:v>
@@ -22021,7 +22021,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="4" t="str">
-        <x:v>R-SHOIN-225</x:v>
+        <x:v>R-REAL-225</x:v>
       </x:c>
       <x:c r="B19" s="4" t="str">
         <x:v>225</x:v>
@@ -22062,7 +22062,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="4" t="str">
-        <x:v>R-SHOIN-225</x:v>
+        <x:v>R-REAL-225</x:v>
       </x:c>
       <x:c r="B20" s="4" t="str">
         <x:v>225</x:v>
@@ -22103,7 +22103,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="4" t="str">
-        <x:v>R-SHOIN-225</x:v>
+        <x:v>R-REAL-225</x:v>
       </x:c>
       <x:c r="B21" s="4" t="str">
         <x:v>225</x:v>
@@ -22144,7 +22144,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="4" t="str">
-        <x:v>R-SHOIN-225</x:v>
+        <x:v>R-REAL-225</x:v>
       </x:c>
       <x:c r="B22" s="4" t="str">
         <x:v>225</x:v>
@@ -22185,7 +22185,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="4" t="str">
-        <x:v>R-SHOIN-225</x:v>
+        <x:v>R-REAL-225</x:v>
       </x:c>
       <x:c r="B23" s="4" t="str">
         <x:v>225</x:v>
@@ -22226,7 +22226,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="4" t="str">
-        <x:v>R-SHOIN-225</x:v>
+        <x:v>R-REAL-225</x:v>
       </x:c>
       <x:c r="B24" s="4" t="str">
         <x:v>225</x:v>
@@ -22267,7 +22267,7 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="4" t="str">
-        <x:v>R-SHOIN-225</x:v>
+        <x:v>R-REAL-225</x:v>
       </x:c>
       <x:c r="B25" s="4" t="str">
         <x:v>225</x:v>
@@ -22308,7 +22308,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="4" t="str">
-        <x:v>R-SHOIN-225</x:v>
+        <x:v>R-REAL-225</x:v>
       </x:c>
       <x:c r="B26" s="4" t="str">
         <x:v>225</x:v>
@@ -22349,7 +22349,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="4" t="str">
-        <x:v>R-SHOIN-225</x:v>
+        <x:v>R-REAL-225</x:v>
       </x:c>
       <x:c r="B27" s="4" t="str">
         <x:v>225</x:v>
@@ -22390,7 +22390,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="4" t="str">
-        <x:v>R-SHOIN-226</x:v>
+        <x:v>R-REAL-226</x:v>
       </x:c>
       <x:c r="B28" s="4" t="str">
         <x:v>226</x:v>
@@ -22431,7 +22431,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="4" t="str">
-        <x:v>R-SHOIN-226</x:v>
+        <x:v>R-REAL-226</x:v>
       </x:c>
       <x:c r="B29" s="4" t="str">
         <x:v>226</x:v>
@@ -22472,7 +22472,7 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="4" t="str">
-        <x:v>R-SHOIN-226</x:v>
+        <x:v>R-REAL-226</x:v>
       </x:c>
       <x:c r="B30" s="4" t="str">
         <x:v>226</x:v>
@@ -22513,7 +22513,7 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="4" t="str">
-        <x:v>R-SHOIN-226</x:v>
+        <x:v>R-REAL-226</x:v>
       </x:c>
       <x:c r="B31" s="4" t="str">
         <x:v>226</x:v>
@@ -22554,7 +22554,7 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="4" t="str">
-        <x:v>R-SHOIN-226</x:v>
+        <x:v>R-REAL-226</x:v>
       </x:c>
       <x:c r="B32" s="4" t="str">
         <x:v>226</x:v>
@@ -22595,7 +22595,7 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="4" t="str">
-        <x:v>R-SHOIN-227</x:v>
+        <x:v>R-REAL-227</x:v>
       </x:c>
       <x:c r="B33" s="4" t="str">
         <x:v>227</x:v>
@@ -22636,7 +22636,7 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="4" t="str">
-        <x:v>R-SHOIN-228</x:v>
+        <x:v>R-REAL-228</x:v>
       </x:c>
       <x:c r="B34" s="4" t="str">
         <x:v>228</x:v>
@@ -22677,7 +22677,7 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="4" t="str">
-        <x:v>R-SHOIN-229</x:v>
+        <x:v>R-REAL-229</x:v>
       </x:c>
       <x:c r="B35" s="4" t="str">
         <x:v>229</x:v>
@@ -22718,7 +22718,7 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="4" t="str">
-        <x:v>R-SHOIN-230</x:v>
+        <x:v>R-REAL-230</x:v>
       </x:c>
       <x:c r="B36" s="4" t="str">
         <x:v>230</x:v>
@@ -22759,7 +22759,7 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="4" t="str">
-        <x:v>R-SHOIN-230</x:v>
+        <x:v>R-REAL-230</x:v>
       </x:c>
       <x:c r="B37" s="4" t="str">
         <x:v>230</x:v>
@@ -22800,7 +22800,7 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="4" t="str">
-        <x:v>R-SHOIN-231</x:v>
+        <x:v>R-REAL-231</x:v>
       </x:c>
       <x:c r="B38" s="4" t="str">
         <x:v>231</x:v>
@@ -22841,7 +22841,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="4" t="str">
-        <x:v>R-SHOIN-239</x:v>
+        <x:v>R-REAL-239</x:v>
       </x:c>
       <x:c r="B39" s="4" t="str">
         <x:v>239</x:v>
@@ -22882,7 +22882,7 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="4" t="str">
-        <x:v>R-SHOIN-236</x:v>
+        <x:v>R-REAL-236</x:v>
       </x:c>
       <x:c r="B40" s="4" t="str">
         <x:v>236</x:v>
@@ -22923,7 +22923,7 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="4" t="str">
-        <x:v>R-SHOIN-238</x:v>
+        <x:v>R-REAL-238</x:v>
       </x:c>
       <x:c r="B41" s="4" t="str">
         <x:v>238</x:v>
@@ -22964,7 +22964,7 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="4" t="str">
-        <x:v>R-SHOIN-232</x:v>
+        <x:v>R-REAL-232</x:v>
       </x:c>
       <x:c r="B42" s="4" t="str">
         <x:v>232</x:v>
@@ -23005,7 +23005,7 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="4" t="str">
-        <x:v>R-SHOIN-237</x:v>
+        <x:v>R-REAL-237</x:v>
       </x:c>
       <x:c r="B43" s="4" t="str">
         <x:v>237</x:v>
@@ -23046,7 +23046,7 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="4" t="str">
-        <x:v>R-SHOIN-237</x:v>
+        <x:v>R-REAL-237</x:v>
       </x:c>
       <x:c r="B44" s="4" t="str">
         <x:v>237</x:v>
@@ -23087,7 +23087,7 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="4" t="str">
-        <x:v>R-SHOIN-232</x:v>
+        <x:v>R-REAL-232</x:v>
       </x:c>
       <x:c r="B45" s="4" t="str">
         <x:v>232</x:v>
@@ -23128,7 +23128,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="4" t="str">
-        <x:v>R-SHOIN-234</x:v>
+        <x:v>R-REAL-234</x:v>
       </x:c>
       <x:c r="B46" s="4" t="str">
         <x:v>234</x:v>
@@ -23169,7 +23169,7 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="4" t="str">
-        <x:v>R-SHOIN-235</x:v>
+        <x:v>R-REAL-235</x:v>
       </x:c>
       <x:c r="B47" s="4" t="str">
         <x:v>235</x:v>
@@ -23210,7 +23210,7 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="4" t="str">
-        <x:v>R-SHOIN-233</x:v>
+        <x:v>R-REAL-233</x:v>
       </x:c>
       <x:c r="B48" s="4" t="str">
         <x:v>233</x:v>
@@ -23251,7 +23251,7 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="4" t="str">
-        <x:v>R-SHOIN-241</x:v>
+        <x:v>R-REAL-241</x:v>
       </x:c>
       <x:c r="B49" s="4" t="str">
         <x:v>241</x:v>
@@ -23292,7 +23292,7 @@
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="4" t="str">
-        <x:v>R-SHOIN-240</x:v>
+        <x:v>R-REAL-240</x:v>
       </x:c>
       <x:c r="B50" s="4" t="str">
         <x:v>240</x:v>
@@ -23333,7 +23333,7 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="4" t="str">
-        <x:v>R-SHOIN-246</x:v>
+        <x:v>R-REAL-246</x:v>
       </x:c>
       <x:c r="B51" s="4" t="str">
         <x:v>246</x:v>
@@ -23374,7 +23374,7 @@
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="4" t="str">
-        <x:v>R-SHOIN-242</x:v>
+        <x:v>R-REAL-242</x:v>
       </x:c>
       <x:c r="B52" s="4" t="str">
         <x:v>242</x:v>
@@ -23415,7 +23415,7 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="4" t="str">
-        <x:v>R-SHOIN-243</x:v>
+        <x:v>R-REAL-243</x:v>
       </x:c>
       <x:c r="B53" s="4" t="str">
         <x:v>243</x:v>
@@ -23456,7 +23456,7 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="4" t="str">
-        <x:v>R-SHOIN-244</x:v>
+        <x:v>R-REAL-244</x:v>
       </x:c>
       <x:c r="B54" s="4" t="str">
         <x:v>244</x:v>
@@ -23497,7 +23497,7 @@
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="4" t="str">
-        <x:v>R-SHOIN-245</x:v>
+        <x:v>R-REAL-245</x:v>
       </x:c>
       <x:c r="B55" s="4" t="str">
         <x:v>245</x:v>
@@ -23538,7 +23538,7 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="4" t="str">
-        <x:v>R-SHOIN-247</x:v>
+        <x:v>R-REAL-247</x:v>
       </x:c>
       <x:c r="B56" s="4" t="str">
         <x:v>247</x:v>
@@ -23579,7 +23579,7 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="4" t="str">
-        <x:v>R-SHOIN-248</x:v>
+        <x:v>R-REAL-248</x:v>
       </x:c>
       <x:c r="B57" s="4" t="str">
         <x:v>248</x:v>
@@ -23620,7 +23620,7 @@
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="4" t="str">
-        <x:v>R-SHOIN-249</x:v>
+        <x:v>R-REAL-249</x:v>
       </x:c>
       <x:c r="B58" s="4" t="str">
         <x:v>249</x:v>
@@ -23661,7 +23661,7 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="4" t="str">
-        <x:v>R-SHOIN-260</x:v>
+        <x:v>R-REAL-260</x:v>
       </x:c>
       <x:c r="B59" s="4" t="str">
         <x:v>260</x:v>
@@ -23702,7 +23702,7 @@
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="4" t="str">
-        <x:v>R-SHOIN-254</x:v>
+        <x:v>R-REAL-254</x:v>
       </x:c>
       <x:c r="B60" s="4" t="str">
         <x:v>254</x:v>
@@ -23743,7 +23743,7 @@
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="4" t="str">
-        <x:v>R-SHOIN-254</x:v>
+        <x:v>R-REAL-254</x:v>
       </x:c>
       <x:c r="B61" s="4" t="str">
         <x:v>254</x:v>
@@ -23784,7 +23784,7 @@
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="4" t="str">
-        <x:v>R-SHOIN-254</x:v>
+        <x:v>R-REAL-254</x:v>
       </x:c>
       <x:c r="B62" s="4" t="str">
         <x:v>254</x:v>
@@ -23825,7 +23825,7 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="4" t="str">
-        <x:v>R-SHOIN-255</x:v>
+        <x:v>R-REAL-255</x:v>
       </x:c>
       <x:c r="B63" s="4" t="str">
         <x:v>255</x:v>
@@ -23866,7 +23866,7 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="4" t="str">
-        <x:v>R-SHOIN-253</x:v>
+        <x:v>R-REAL-253</x:v>
       </x:c>
       <x:c r="B64" s="4" t="str">
         <x:v>253</x:v>
@@ -23907,7 +23907,7 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="4" t="str">
-        <x:v>R-SHOIN-262</x:v>
+        <x:v>R-REAL-262</x:v>
       </x:c>
       <x:c r="B65" s="4" t="str">
         <x:v>262</x:v>
@@ -23948,7 +23948,7 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="4" t="str">
-        <x:v>R-SHOIN-256</x:v>
+        <x:v>R-REAL-256</x:v>
       </x:c>
       <x:c r="B66" s="4" t="str">
         <x:v>256</x:v>
@@ -23989,7 +23989,7 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="4" t="str">
-        <x:v>R-SHOIN-256</x:v>
+        <x:v>R-REAL-256</x:v>
       </x:c>
       <x:c r="B67" s="4" t="str">
         <x:v>256</x:v>
@@ -24030,7 +24030,7 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="4" t="str">
-        <x:v>R-SHOIN-259</x:v>
+        <x:v>R-REAL-259</x:v>
       </x:c>
       <x:c r="B68" s="4" t="str">
         <x:v>259</x:v>
@@ -24071,7 +24071,7 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="4" t="str">
-        <x:v>R-SHOIN-257</x:v>
+        <x:v>R-REAL-257</x:v>
       </x:c>
       <x:c r="B69" s="4" t="str">
         <x:v>257</x:v>
@@ -24112,7 +24112,7 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="4" t="str">
-        <x:v>R-SHOIN-261</x:v>
+        <x:v>R-REAL-261</x:v>
       </x:c>
       <x:c r="B70" s="4" t="str">
         <x:v>261</x:v>
@@ -24153,7 +24153,7 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="4" t="str">
-        <x:v>R-SHOIN-263</x:v>
+        <x:v>R-REAL-263</x:v>
       </x:c>
       <x:c r="B71" s="4" t="str">
         <x:v>263</x:v>
@@ -24194,7 +24194,7 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="4" t="str">
-        <x:v>R-SHOIN-258</x:v>
+        <x:v>R-REAL-258</x:v>
       </x:c>
       <x:c r="B72" s="4" t="str">
         <x:v>258</x:v>
@@ -24235,7 +24235,7 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="4" t="str">
-        <x:v>R-SHOIN-250</x:v>
+        <x:v>R-REAL-250</x:v>
       </x:c>
       <x:c r="B73" s="4" t="str">
         <x:v>250</x:v>
@@ -24276,7 +24276,7 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="4" t="str">
-        <x:v>R-SHOIN-17</x:v>
+        <x:v>R-REAL-17</x:v>
       </x:c>
       <x:c r="B74" s="4" t="str">
         <x:v>17</x:v>
@@ -24317,7 +24317,7 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="4" t="str">
-        <x:v>R-SHOIN-17</x:v>
+        <x:v>R-REAL-17</x:v>
       </x:c>
       <x:c r="B75" s="4" t="str">
         <x:v>17</x:v>
@@ -24358,7 +24358,7 @@
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="4" t="str">
-        <x:v>R-SHOIN-18</x:v>
+        <x:v>R-REAL-18</x:v>
       </x:c>
       <x:c r="B76" s="4" t="str">
         <x:v>18</x:v>
@@ -24399,7 +24399,7 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="4" t="str">
-        <x:v>R-SHOIN-18</x:v>
+        <x:v>R-REAL-18</x:v>
       </x:c>
       <x:c r="B77" s="4" t="str">
         <x:v>18</x:v>
@@ -24440,7 +24440,7 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="4" t="str">
-        <x:v>R-SHOIN-18</x:v>
+        <x:v>R-REAL-18</x:v>
       </x:c>
       <x:c r="B78" s="4" t="str">
         <x:v>18</x:v>
@@ -24481,7 +24481,7 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="4" t="str">
-        <x:v>R-SHOIN-18</x:v>
+        <x:v>R-REAL-18</x:v>
       </x:c>
       <x:c r="B79" s="4" t="str">
         <x:v>18</x:v>
@@ -24522,7 +24522,7 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="4" t="str">
-        <x:v>R-SHOIN-18</x:v>
+        <x:v>R-REAL-18</x:v>
       </x:c>
       <x:c r="B80" s="4" t="str">
         <x:v>18</x:v>
@@ -24563,7 +24563,7 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B81" s="4" t="str">
         <x:v>19</x:v>
@@ -24604,7 +24604,7 @@
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B82" s="4" t="str">
         <x:v>19</x:v>
@@ -24645,7 +24645,7 @@
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B83" s="4" t="str">
         <x:v>19</x:v>
@@ -24686,7 +24686,7 @@
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B84" s="4" t="str">
         <x:v>19</x:v>
@@ -24727,7 +24727,7 @@
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B85" s="4" t="str">
         <x:v>19</x:v>
@@ -24768,7 +24768,7 @@
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B86" s="4" t="str">
         <x:v>19</x:v>
@@ -24809,7 +24809,7 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B87" s="4" t="str">
         <x:v>19</x:v>
@@ -24850,7 +24850,7 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B88" s="4" t="str">
         <x:v>19</x:v>
@@ -24891,7 +24891,7 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B89" s="4" t="str">
         <x:v>19</x:v>
@@ -24932,7 +24932,7 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B90" s="4" t="str">
         <x:v>19</x:v>
@@ -24973,7 +24973,7 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B91" s="4" t="str">
         <x:v>19</x:v>
@@ -25014,7 +25014,7 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B92" s="4" t="str">
         <x:v>19</x:v>
@@ -25055,7 +25055,7 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B93" s="4" t="str">
         <x:v>19</x:v>
@@ -25096,7 +25096,7 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B94" s="4" t="str">
         <x:v>19</x:v>
@@ -25137,7 +25137,7 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B95" s="4" t="str">
         <x:v>19</x:v>
@@ -25178,7 +25178,7 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B96" s="4" t="str">
         <x:v>19</x:v>
@@ -25219,7 +25219,7 @@
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B97" s="4" t="str">
         <x:v>19</x:v>
@@ -25260,7 +25260,7 @@
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="4" t="str">
-        <x:v>R-SHOIN-19</x:v>
+        <x:v>R-REAL-19</x:v>
       </x:c>
       <x:c r="B98" s="4" t="str">
         <x:v>19</x:v>
@@ -25301,7 +25301,7 @@
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="4" t="str">
-        <x:v>R-SHOIN-20</x:v>
+        <x:v>R-REAL-20</x:v>
       </x:c>
       <x:c r="B99" s="4" t="str">
         <x:v>20</x:v>
@@ -25342,7 +25342,7 @@
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="4" t="str">
-        <x:v>R-SHOIN-20</x:v>
+        <x:v>R-REAL-20</x:v>
       </x:c>
       <x:c r="B100" s="4" t="str">
         <x:v>20</x:v>
@@ -25383,7 +25383,7 @@
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="4" t="str">
-        <x:v>R-SHOIN-20</x:v>
+        <x:v>R-REAL-20</x:v>
       </x:c>
       <x:c r="B101" s="4" t="str">
         <x:v>20</x:v>
@@ -25424,7 +25424,7 @@
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="4" t="str">
-        <x:v>R-SHOIN-20</x:v>
+        <x:v>R-REAL-20</x:v>
       </x:c>
       <x:c r="B102" s="4" t="str">
         <x:v>20</x:v>
@@ -25465,7 +25465,7 @@
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="4" t="str">
-        <x:v>R-SHOIN-20</x:v>
+        <x:v>R-REAL-20</x:v>
       </x:c>
       <x:c r="B103" s="4" t="str">
         <x:v>20</x:v>
@@ -25506,7 +25506,7 @@
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="4" t="str">
-        <x:v>R-SHOIN-20</x:v>
+        <x:v>R-REAL-20</x:v>
       </x:c>
       <x:c r="B104" s="4" t="str">
         <x:v>20</x:v>
@@ -25547,7 +25547,7 @@
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="4" t="str">
-        <x:v>R-SHOIN-20</x:v>
+        <x:v>R-REAL-20</x:v>
       </x:c>
       <x:c r="B105" s="4" t="str">
         <x:v>20</x:v>
@@ -25588,7 +25588,7 @@
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="4" t="str">
-        <x:v>R-SHOIN-20</x:v>
+        <x:v>R-REAL-20</x:v>
       </x:c>
       <x:c r="B106" s="4" t="str">
         <x:v>20</x:v>
@@ -25629,7 +25629,7 @@
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="4" t="str">
-        <x:v>R-SHOIN-21</x:v>
+        <x:v>R-REAL-21</x:v>
       </x:c>
       <x:c r="B107" s="4" t="str">
         <x:v>21</x:v>
@@ -25670,7 +25670,7 @@
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="4" t="str">
-        <x:v>R-SHOIN-21</x:v>
+        <x:v>R-REAL-21</x:v>
       </x:c>
       <x:c r="B108" s="4" t="str">
         <x:v>21</x:v>
@@ -25711,7 +25711,7 @@
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="4" t="str">
-        <x:v>R-SHOIN-21</x:v>
+        <x:v>R-REAL-21</x:v>
       </x:c>
       <x:c r="B109" s="4" t="str">
         <x:v>21</x:v>
@@ -25752,7 +25752,7 @@
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="4" t="str">
-        <x:v>R-SHOIN-21</x:v>
+        <x:v>R-REAL-21</x:v>
       </x:c>
       <x:c r="B110" s="4" t="str">
         <x:v>21</x:v>
@@ -25793,7 +25793,7 @@
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="4" t="str">
-        <x:v>R-SHOIN-21</x:v>
+        <x:v>R-REAL-21</x:v>
       </x:c>
       <x:c r="B111" s="4" t="str">
         <x:v>21</x:v>
@@ -25834,7 +25834,7 @@
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="4" t="str">
-        <x:v>R-SHOIN-21</x:v>
+        <x:v>R-REAL-21</x:v>
       </x:c>
       <x:c r="B112" s="4" t="str">
         <x:v>21</x:v>
@@ -25875,7 +25875,7 @@
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="4" t="str">
-        <x:v>R-SHOIN-23</x:v>
+        <x:v>R-REAL-23</x:v>
       </x:c>
       <x:c r="B113" s="4" t="str">
         <x:v>23</x:v>
@@ -25916,7 +25916,7 @@
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="4" t="str">
-        <x:v>R-SHOIN-61</x:v>
+        <x:v>R-REAL-61</x:v>
       </x:c>
       <x:c r="B114" s="4" t="str">
         <x:v>61</x:v>
@@ -25957,7 +25957,7 @@
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="4" t="str">
-        <x:v>R-SHOIN-52</x:v>
+        <x:v>R-REAL-52</x:v>
       </x:c>
       <x:c r="B115" s="4" t="str">
         <x:v>52</x:v>
@@ -25998,7 +25998,7 @@
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="4" t="str">
-        <x:v>R-SHOIN-58</x:v>
+        <x:v>R-REAL-58</x:v>
       </x:c>
       <x:c r="B116" s="4" t="str">
         <x:v>58</x:v>
@@ -26039,7 +26039,7 @@
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="4" t="str">
-        <x:v>R-SHOIN-30</x:v>
+        <x:v>R-REAL-30</x:v>
       </x:c>
       <x:c r="B117" s="4" t="str">
         <x:v>30</x:v>
@@ -26080,7 +26080,7 @@
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="4" t="str">
-        <x:v>R-SHOIN-64</x:v>
+        <x:v>R-REAL-64</x:v>
       </x:c>
       <x:c r="B118" s="4" t="str">
         <x:v>64</x:v>
@@ -26121,7 +26121,7 @@
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="4" t="str">
-        <x:v>R-SHOIN-32</x:v>
+        <x:v>R-REAL-32</x:v>
       </x:c>
       <x:c r="B119" s="4" t="str">
         <x:v>32</x:v>
@@ -26162,7 +26162,7 @@
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="4" t="str">
-        <x:v>R-SHOIN-63</x:v>
+        <x:v>R-REAL-63</x:v>
       </x:c>
       <x:c r="B120" s="4" t="str">
         <x:v>63</x:v>
@@ -26203,7 +26203,7 @@
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="4" t="str">
-        <x:v>R-SHOIN-31</x:v>
+        <x:v>R-REAL-31</x:v>
       </x:c>
       <x:c r="B121" s="4" t="str">
         <x:v>31</x:v>
@@ -26244,7 +26244,7 @@
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="4" t="str">
-        <x:v>R-SHOIN-26</x:v>
+        <x:v>R-REAL-26</x:v>
       </x:c>
       <x:c r="B122" s="4" t="str">
         <x:v>26</x:v>
@@ -26285,7 +26285,7 @@
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="4" t="str">
-        <x:v>R-SHOIN-37</x:v>
+        <x:v>R-REAL-37</x:v>
       </x:c>
       <x:c r="B123" s="4" t="str">
         <x:v>37</x:v>
@@ -26326,7 +26326,7 @@
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="4" t="str">
-        <x:v>R-SHOIN-57</x:v>
+        <x:v>R-REAL-57</x:v>
       </x:c>
       <x:c r="B124" s="4" t="str">
         <x:v>57</x:v>
@@ -26367,7 +26367,7 @@
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="4" t="str">
-        <x:v>R-SHOIN-45</x:v>
+        <x:v>R-REAL-45</x:v>
       </x:c>
       <x:c r="B125" s="4" t="str">
         <x:v>45</x:v>
@@ -26408,7 +26408,7 @@
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="4" t="str">
-        <x:v>R-SHOIN-24</x:v>
+        <x:v>R-REAL-24</x:v>
       </x:c>
       <x:c r="B126" s="4" t="str">
         <x:v>24</x:v>
@@ -26449,7 +26449,7 @@
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="4" t="str">
-        <x:v>R-SHOIN-33</x:v>
+        <x:v>R-REAL-33</x:v>
       </x:c>
       <x:c r="B127" s="4" t="str">
         <x:v>33</x:v>
@@ -26490,7 +26490,7 @@
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="4" t="str">
-        <x:v>R-SHOIN-34</x:v>
+        <x:v>R-REAL-34</x:v>
       </x:c>
       <x:c r="B128" s="4" t="str">
         <x:v>34</x:v>
@@ -26531,7 +26531,7 @@
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="4" t="str">
-        <x:v>R-SHOIN-25</x:v>
+        <x:v>R-REAL-25</x:v>
       </x:c>
       <x:c r="B129" s="4" t="str">
         <x:v>25</x:v>
@@ -26572,7 +26572,7 @@
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="4" t="str">
-        <x:v>R-SHOIN-25</x:v>
+        <x:v>R-REAL-25</x:v>
       </x:c>
       <x:c r="B130" s="4" t="str">
         <x:v>25</x:v>
@@ -26613,7 +26613,7 @@
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="4" t="str">
-        <x:v>R-SHOIN-54</x:v>
+        <x:v>R-REAL-54</x:v>
       </x:c>
       <x:c r="B131" s="4" t="str">
         <x:v>54</x:v>
@@ -26654,7 +26654,7 @@
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="4" t="str">
-        <x:v>R-SHOIN-65</x:v>
+        <x:v>R-REAL-65</x:v>
       </x:c>
       <x:c r="B132" s="4" t="str">
         <x:v>65</x:v>
@@ -26695,7 +26695,7 @@
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="4" t="str">
-        <x:v>R-SHOIN-65</x:v>
+        <x:v>R-REAL-65</x:v>
       </x:c>
       <x:c r="B133" s="4" t="str">
         <x:v>65</x:v>
@@ -26736,7 +26736,7 @@
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="4" t="str">
-        <x:v>R-SHOIN-39</x:v>
+        <x:v>R-REAL-39</x:v>
       </x:c>
       <x:c r="B134" s="4" t="str">
         <x:v>39</x:v>
@@ -26777,7 +26777,7 @@
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="4" t="str">
-        <x:v>R-SHOIN-42</x:v>
+        <x:v>R-REAL-42</x:v>
       </x:c>
       <x:c r="B135" s="4" t="str">
         <x:v>42</x:v>
@@ -26818,7 +26818,7 @@
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="4" t="str">
-        <x:v>R-SHOIN-41</x:v>
+        <x:v>R-REAL-41</x:v>
       </x:c>
       <x:c r="B136" s="4" t="str">
         <x:v>41</x:v>
@@ -26859,7 +26859,7 @@
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="4" t="str">
-        <x:v>R-SHOIN-49</x:v>
+        <x:v>R-REAL-49</x:v>
       </x:c>
       <x:c r="B137" s="4" t="str">
         <x:v>49</x:v>
@@ -26900,7 +26900,7 @@
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="4" t="str">
-        <x:v>R-SHOIN-28</x:v>
+        <x:v>R-REAL-28</x:v>
       </x:c>
       <x:c r="B138" s="4" t="str">
         <x:v>28</x:v>
@@ -26941,7 +26941,7 @@
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="4" t="str">
-        <x:v>R-SHOIN-66</x:v>
+        <x:v>R-REAL-66</x:v>
       </x:c>
       <x:c r="B139" s="4" t="str">
         <x:v>66</x:v>
@@ -26982,7 +26982,7 @@
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="4" t="str">
-        <x:v>R-SHOIN-44</x:v>
+        <x:v>R-REAL-44</x:v>
       </x:c>
       <x:c r="B140" s="4" t="str">
         <x:v>44</x:v>
@@ -27023,7 +27023,7 @@
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="4" t="str">
-        <x:v>R-SHOIN-36</x:v>
+        <x:v>R-REAL-36</x:v>
       </x:c>
       <x:c r="B141" s="4" t="str">
         <x:v>36</x:v>
@@ -27064,7 +27064,7 @@
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="4" t="str">
-        <x:v>R-SHOIN-43</x:v>
+        <x:v>R-REAL-43</x:v>
       </x:c>
       <x:c r="B142" s="4" t="str">
         <x:v>43</x:v>
@@ -27105,7 +27105,7 @@
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="4" t="str">
-        <x:v>R-SHOIN-67</x:v>
+        <x:v>R-REAL-67</x:v>
       </x:c>
       <x:c r="B143" s="4" t="str">
         <x:v>67</x:v>
@@ -27146,7 +27146,7 @@
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="4" t="str">
-        <x:v>R-SHOIN-38</x:v>
+        <x:v>R-REAL-38</x:v>
       </x:c>
       <x:c r="B144" s="4" t="str">
         <x:v>38</x:v>
@@ -27187,7 +27187,7 @@
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="4" t="str">
-        <x:v>R-SHOIN-46</x:v>
+        <x:v>R-REAL-46</x:v>
       </x:c>
       <x:c r="B145" s="4" t="str">
         <x:v>46</x:v>
@@ -27228,7 +27228,7 @@
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="4" t="str">
-        <x:v>R-SHOIN-47</x:v>
+        <x:v>R-REAL-47</x:v>
       </x:c>
       <x:c r="B146" s="4" t="str">
         <x:v>47</x:v>
@@ -27269,7 +27269,7 @@
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="4" t="str">
-        <x:v>R-SHOIN-48</x:v>
+        <x:v>R-REAL-48</x:v>
       </x:c>
       <x:c r="B147" s="4" t="str">
         <x:v>48</x:v>
@@ -27310,7 +27310,7 @@
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="4" t="str">
-        <x:v>R-SHOIN-309</x:v>
+        <x:v>R-REAL-309</x:v>
       </x:c>
       <x:c r="B148" s="4" t="str">
         <x:v>309</x:v>
@@ -27351,7 +27351,7 @@
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="4" t="str">
-        <x:v>R-SHOIN-60</x:v>
+        <x:v>R-REAL-60</x:v>
       </x:c>
       <x:c r="B149" s="4" t="str">
         <x:v>60</x:v>
@@ -27392,7 +27392,7 @@
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="4" t="str">
-        <x:v>R-SHOIN-51</x:v>
+        <x:v>R-REAL-51</x:v>
       </x:c>
       <x:c r="B150" s="4" t="str">
         <x:v>51</x:v>
@@ -27433,7 +27433,7 @@
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="4" t="str">
-        <x:v>R-SHOIN-50</x:v>
+        <x:v>R-REAL-50</x:v>
       </x:c>
       <x:c r="B151" s="4" t="str">
         <x:v>50</x:v>
@@ -27474,7 +27474,7 @@
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="4" t="str">
-        <x:v>R-SHOIN-55</x:v>
+        <x:v>R-REAL-55</x:v>
       </x:c>
       <x:c r="B152" s="4" t="str">
         <x:v>55</x:v>
@@ -27515,7 +27515,7 @@
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="4" t="str">
-        <x:v>R-SHOIN-59</x:v>
+        <x:v>R-REAL-59</x:v>
       </x:c>
       <x:c r="B153" s="4" t="str">
         <x:v>59</x:v>
@@ -27556,7 +27556,7 @@
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="4" t="str">
-        <x:v>R-SHOIN-40</x:v>
+        <x:v>R-REAL-40</x:v>
       </x:c>
       <x:c r="B154" s="4" t="str">
         <x:v>40</x:v>
@@ -27597,7 +27597,7 @@
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="4" t="str">
-        <x:v>R-SHOIN-53</x:v>
+        <x:v>R-REAL-53</x:v>
       </x:c>
       <x:c r="B155" s="4" t="str">
         <x:v>53</x:v>
@@ -27638,7 +27638,7 @@
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="4" t="str">
-        <x:v>R-SHOIN-56</x:v>
+        <x:v>R-REAL-56</x:v>
       </x:c>
       <x:c r="B156" s="4" t="str">
         <x:v>56</x:v>
@@ -27679,7 +27679,7 @@
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="4" t="str">
-        <x:v>R-SHOIN-62</x:v>
+        <x:v>R-REAL-62</x:v>
       </x:c>
       <x:c r="B157" s="4" t="str">
         <x:v>62</x:v>
@@ -27720,7 +27720,7 @@
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="4" t="str">
-        <x:v>R-SHOIN-27</x:v>
+        <x:v>R-REAL-27</x:v>
       </x:c>
       <x:c r="B158" s="4" t="str">
         <x:v>27</x:v>
@@ -27761,7 +27761,7 @@
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="4" t="str">
-        <x:v>R-SHOIN-86</x:v>
+        <x:v>R-REAL-86</x:v>
       </x:c>
       <x:c r="B159" s="4" t="str">
         <x:v>86</x:v>
@@ -27802,7 +27802,7 @@
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="4" t="str">
-        <x:v>R-SHOIN-87</x:v>
+        <x:v>R-REAL-87</x:v>
       </x:c>
       <x:c r="B160" s="4" t="str">
         <x:v>87</x:v>
@@ -27843,7 +27843,7 @@
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="4" t="str">
-        <x:v>R-SHOIN-85</x:v>
+        <x:v>R-REAL-85</x:v>
       </x:c>
       <x:c r="B161" s="4" t="str">
         <x:v>85</x:v>
@@ -27884,7 +27884,7 @@
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="4" t="str">
-        <x:v>R-SHOIN-84</x:v>
+        <x:v>R-REAL-84</x:v>
       </x:c>
       <x:c r="B162" s="4" t="str">
         <x:v>84</x:v>
@@ -27925,7 +27925,7 @@
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="4" t="str">
-        <x:v>R-SHOIN-83</x:v>
+        <x:v>R-REAL-83</x:v>
       </x:c>
       <x:c r="B163" s="4" t="str">
         <x:v>83</x:v>
@@ -27966,7 +27966,7 @@
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="4" t="str">
-        <x:v>R-SHOIN-310</x:v>
+        <x:v>R-REAL-310</x:v>
       </x:c>
       <x:c r="B164" s="4" t="str">
         <x:v>310</x:v>
@@ -28007,7 +28007,7 @@
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="4" t="str">
-        <x:v>R-SHOIN-310</x:v>
+        <x:v>R-REAL-310</x:v>
       </x:c>
       <x:c r="B165" s="4" t="str">
         <x:v>310</x:v>
@@ -28048,7 +28048,7 @@
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="4" t="str">
-        <x:v>R-SHOIN-82</x:v>
+        <x:v>R-REAL-82</x:v>
       </x:c>
       <x:c r="B166" s="4" t="str">
         <x:v>82</x:v>
@@ -28089,7 +28089,7 @@
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="4" t="str">
-        <x:v>R-SHOIN-82</x:v>
+        <x:v>R-REAL-82</x:v>
       </x:c>
       <x:c r="B167" s="4" t="str">
         <x:v>82</x:v>
@@ -28130,7 +28130,7 @@
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="4" t="str">
-        <x:v>R-SHOIN-82</x:v>
+        <x:v>R-REAL-82</x:v>
       </x:c>
       <x:c r="B168" s="4" t="str">
         <x:v>82</x:v>
@@ -28171,7 +28171,7 @@
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="4" t="str">
-        <x:v>R-SHOIN-68</x:v>
+        <x:v>R-REAL-68</x:v>
       </x:c>
       <x:c r="B169" s="4" t="str">
         <x:v>68</x:v>
@@ -28212,7 +28212,7 @@
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="4" t="str">
-        <x:v>R-SHOIN-77</x:v>
+        <x:v>R-REAL-77</x:v>
       </x:c>
       <x:c r="B170" s="4" t="str">
         <x:v>77</x:v>
@@ -28253,7 +28253,7 @@
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="4" t="str">
-        <x:v>R-SHOIN-76</x:v>
+        <x:v>R-REAL-76</x:v>
       </x:c>
       <x:c r="B171" s="4" t="str">
         <x:v>76</x:v>
@@ -28294,7 +28294,7 @@
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="4" t="str">
-        <x:v>R-SHOIN-73</x:v>
+        <x:v>R-REAL-73</x:v>
       </x:c>
       <x:c r="B172" s="4" t="str">
         <x:v>73</x:v>
@@ -28335,7 +28335,7 @@
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="4" t="str">
-        <x:v>R-SHOIN-74</x:v>
+        <x:v>R-REAL-74</x:v>
       </x:c>
       <x:c r="B173" s="4" t="str">
         <x:v>74</x:v>
@@ -28376,7 +28376,7 @@
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="4" t="str">
-        <x:v>R-SHOIN-72</x:v>
+        <x:v>R-REAL-72</x:v>
       </x:c>
       <x:c r="B174" s="4" t="str">
         <x:v>72</x:v>
@@ -28417,7 +28417,7 @@
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="4" t="str">
-        <x:v>R-SHOIN-70</x:v>
+        <x:v>R-REAL-70</x:v>
       </x:c>
       <x:c r="B175" s="4" t="str">
         <x:v>70</x:v>
@@ -28458,7 +28458,7 @@
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="4" t="str">
-        <x:v>R-SHOIN-70</x:v>
+        <x:v>R-REAL-70</x:v>
       </x:c>
       <x:c r="B176" s="4" t="str">
         <x:v>70</x:v>
@@ -28499,7 +28499,7 @@
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="4" t="str">
-        <x:v>R-SHOIN-70</x:v>
+        <x:v>R-REAL-70</x:v>
       </x:c>
       <x:c r="B177" s="4" t="str">
         <x:v>70</x:v>
@@ -28540,7 +28540,7 @@
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="4" t="str">
-        <x:v>R-SHOIN-69</x:v>
+        <x:v>R-REAL-69</x:v>
       </x:c>
       <x:c r="B178" s="4" t="str">
         <x:v>69</x:v>
@@ -28581,7 +28581,7 @@
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="4" t="str">
-        <x:v>R-SHOIN-88</x:v>
+        <x:v>R-REAL-88</x:v>
       </x:c>
       <x:c r="B179" s="4" t="str">
         <x:v>88</x:v>
@@ -28622,7 +28622,7 @@
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="4" t="str">
-        <x:v>R-SHOIN-88</x:v>
+        <x:v>R-REAL-88</x:v>
       </x:c>
       <x:c r="B180" s="4" t="str">
         <x:v>88</x:v>
@@ -28663,7 +28663,7 @@
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="4" t="str">
-        <x:v>R-SHOIN-79</x:v>
+        <x:v>R-REAL-79</x:v>
       </x:c>
       <x:c r="B181" s="4" t="str">
         <x:v>79</x:v>
@@ -28704,7 +28704,7 @@
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="4" t="str">
-        <x:v>R-SHOIN-93</x:v>
+        <x:v>R-REAL-93</x:v>
       </x:c>
       <x:c r="B182" s="4" t="str">
         <x:v>93</x:v>
@@ -28745,7 +28745,7 @@
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="4" t="str">
-        <x:v>R-SHOIN-78</x:v>
+        <x:v>R-REAL-78</x:v>
       </x:c>
       <x:c r="B183" s="4" t="str">
         <x:v>78</x:v>
@@ -28786,7 +28786,7 @@
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="4" t="str">
-        <x:v>R-SHOIN-71</x:v>
+        <x:v>R-REAL-71</x:v>
       </x:c>
       <x:c r="B184" s="4" t="str">
         <x:v>71</x:v>
@@ -28827,7 +28827,7 @@
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="4" t="str">
-        <x:v>R-SHOIN-15</x:v>
+        <x:v>R-REAL-15</x:v>
       </x:c>
       <x:c r="B185" s="4" t="str">
         <x:v>15</x:v>
@@ -28868,7 +28868,7 @@
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="4" t="str">
-        <x:v>R-SHOIN-15</x:v>
+        <x:v>R-REAL-15</x:v>
       </x:c>
       <x:c r="B186" s="4" t="str">
         <x:v>15</x:v>
@@ -28909,7 +28909,7 @@
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="4" t="str">
-        <x:v>R-SHOIN-15</x:v>
+        <x:v>R-REAL-15</x:v>
       </x:c>
       <x:c r="B187" s="4" t="str">
         <x:v>15</x:v>
@@ -28950,7 +28950,7 @@
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="4" t="str">
-        <x:v>R-SHOIN-15</x:v>
+        <x:v>R-REAL-15</x:v>
       </x:c>
       <x:c r="B188" s="4" t="str">
         <x:v>15</x:v>
@@ -28991,7 +28991,7 @@
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="4" t="str">
-        <x:v>R-SHOIN-15</x:v>
+        <x:v>R-REAL-15</x:v>
       </x:c>
       <x:c r="B189" s="4" t="str">
         <x:v>15</x:v>
@@ -29032,7 +29032,7 @@
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="4" t="str">
-        <x:v>R-SHOIN-15</x:v>
+        <x:v>R-REAL-15</x:v>
       </x:c>
       <x:c r="B190" s="4" t="str">
         <x:v>15</x:v>
@@ -29073,7 +29073,7 @@
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="4" t="str">
-        <x:v>R-SHOIN-15</x:v>
+        <x:v>R-REAL-15</x:v>
       </x:c>
       <x:c r="B191" s="4" t="str">
         <x:v>15</x:v>
@@ -29114,7 +29114,7 @@
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="4" t="str">
-        <x:v>R-SHOIN-16</x:v>
+        <x:v>R-REAL-16</x:v>
       </x:c>
       <x:c r="B192" s="4" t="str">
         <x:v>16</x:v>
@@ -29155,7 +29155,7 @@
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="4" t="str">
-        <x:v>R-SHOIN-16</x:v>
+        <x:v>R-REAL-16</x:v>
       </x:c>
       <x:c r="B193" s="4" t="str">
         <x:v>16</x:v>
